--- a/output/central_unit_requests/LandR - end-2026 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/LandR - end-2026 sustainability reporting request.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Reporting template" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. OPTIONAL highlighted stories" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. SR25 responses" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,6 +43,32 @@
       <sz val="22"/>
     </font>
     <font>
+      <name val="Aptos Narrow"/>
+      <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="000563C1"/>
+      <u val="single"/>
+    </font>
+    <font>
       <name val="Aptos"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
@@ -80,12 +107,6 @@
       <sz val="14"/>
     </font>
     <font>
-      <name val="Aptos"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="12"/>
-    </font>
-    <font>
       <name val="Aptos Narrow"/>
       <b val="1"/>
       <color rgb="000E2841"/>
@@ -100,11 +121,9 @@
     <font>
       <name val="Aptos Narrow"/>
       <b val="1"/>
+      <color rgb="000563C1"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <sz val="11"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="7">
@@ -116,7 +135,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="000B3040"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C1E4F5"/>
       </patternFill>
     </fill>
     <fill>
@@ -126,17 +155,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C1E4F5"/>
       </patternFill>
     </fill>
   </fills>
@@ -147,12 +166,6 @@
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
     </border>
     <border>
       <left style="thin">
@@ -168,62 +181,73 @@
         <color rgb="00808080"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -599,7 +623,7 @@
     <col width="38" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
-    <col hidden="1" outlineLevel="1" width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col hidden="1" outlineLevel="1" width="16" customWidth="1" min="9" max="9"/>
     <col hidden="1" outlineLevel="1" width="50" customWidth="1" min="10" max="10"/>
     <col hidden="1" outlineLevel="1" width="24" customWidth="1" min="11" max="11"/>
@@ -650,7 +674,7 @@
 • Provide commentary on progress towards each target (Column M or N)
 • Provide supporting documentation if required (Column O), including links to images
 • Note the source of your information and any limitations (Column P), then confirm the information is accurate (Columns Q–R)
-• Your end-2025 responses (where a related target existed) can be viewed by clicking the [+] icon above Columns H–K
+• Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
 • 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch.
 • Due: Friday 15 January 2027 (TBC). Questions: Sustainability Strategy team (sustainability-strategy@unimelb.edu.au – TBC)</t>
@@ -728,7 +752,7 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>End-2025 reporting (for reference – click [+] above to expand)</t>
+          <t>End-2025 reporting (click the ref to see your full SR25 response; [+] above expands a summary)</t>
         </is>
       </c>
       <c r="L13" s="13" t="inlineStr">
@@ -903,7 +927,8 @@
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>Provide update of University maturity assesment. Include maturity ratings, key gaps and priority improvement actions.when available</t>
+          <t>In end-2025 reporting your area reported on the related SP2030 target 8a(i) and rated it 'Met or exceeded' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
+Provide update of University maturity assesment. Include maturity ratings, key gaps and priority improvement actions.when available</t>
         </is>
       </c>
       <c r="G16" s="19" t="inlineStr">
@@ -911,10 +936,29 @@
           <t>We will report the University's climate-change resilience maturity rating, key gaps and priority actions in the 2026 Sustainability Report (building on the Climate Change Preparedness Framework assessment reported in 2025).</t>
         </is>
       </c>
-      <c r="H16" s="19" t="inlineStr"/>
-      <c r="I16" s="19" t="inlineStr"/>
-      <c r="J16" s="19" t="inlineStr"/>
-      <c r="K16" s="19" t="inlineStr"/>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>8a(i)
+→ view SR25 response</t>
+        </is>
+      </c>
+      <c r="I16" s="19" t="inlineStr">
+        <is>
+          <t>Met or exceeded</t>
+        </is>
+      </c>
+      <c r="J16" s="19" t="inlineStr">
+        <is>
+          <t>Review of University Risk 16 Climate Change was completed in Nov 2025, as part of the annual review cycle.
+The review identified a positive trend, showing improved levels of climate‑change preparedness, with work underway to complete the end‑of‑2025 assessment.</t>
+        </is>
+      </c>
+      <c r="K16" s="19" t="inlineStr">
+        <is>
+          <t>All University risks including Risk 16 Climate Change were presented to RMCC and ARC in Nov 25 for their oversight.
+There will be a risk presentation of Risk 16 Climate Change at RMCC Meeting 1 in Feb 2026.</t>
+        </is>
+      </c>
       <c r="L16" s="19" t="n"/>
       <c r="M16" s="19" t="n"/>
       <c r="N16" s="19" t="n"/>
@@ -944,6 +988,9 @@
       <formula1>=Lists!$C$2:$C$4</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="H16" location="'3. SR25 responses'!B7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -994,7 +1041,7 @@
           <t>How to use this spreadsheet</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Friday 4 December 2026 (TBC) (early submission helps us develop case studies).</t>
         </is>
@@ -1002,47 +1049,47 @@
     </row>
     <row r="6"/>
     <row r="8">
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>Related Sustainability 2030 targets (optional)</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>Images and other media</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>Links and supporting documentation</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
-      <c r="B9" s="22" t="inlineStr"/>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr"/>
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>• Please include a brief description of a project or activity that has made a significant contribution to sustainability at the University (up to 250 words)
 • Summarise the benefits. Benefits may relate to operational outcomes, environmental/social outcomes, and sector benefits.</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr"/>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr"/>
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>(link to OneDrive/SharePoint files or published online content preferred)</t>
         </is>
       </c>
-      <c r="F9" s="22" t="inlineStr"/>
+      <c r="F9" s="23" t="inlineStr"/>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" t="n">
@@ -1291,4 +1338,193 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>End-2025 target status assessment and reporting (for reference)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Your SR25 responses – Legal and Risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="B3" s="21" t="inlineStr">
+        <is>
+          <t>Your responses to the end-2025 reporting request, against the former Sustainability Plan 2030 (SP2030) targets. For reference only – please do not edit. Use the 'Back to request' links to return to the reporting template.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>← Back to request</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>Legal and Risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>SR25 ref</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>SP2030 target</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>2025 reporting request</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>Confirmed end-2025 status</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>OPTION 1: Target-level reporting</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>OPTION 2: Indicator-level reporting</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>Supporting information/comments</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>Related SR26 indicator(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="160" customHeight="1">
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>8a(i)</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>The University reaches and maintains a 'high' climate change preparedness level</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>Assessment based on the Climate Change Preparedness Framework</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>Met or exceeded</t>
+        </is>
+      </c>
+      <c r="F7" s="19" t="inlineStr"/>
+      <c r="G7" s="19" t="inlineStr">
+        <is>
+          <t>Review of University Risk 16 Climate Change was completed in Nov 2025, as part of the annual review cycle.
+The review identified a positive trend, showing improved levels of climate‑change preparedness, with work underway to complete the end‑of‑2025 assessment.</t>
+        </is>
+      </c>
+      <c r="H7" s="19" t="inlineStr">
+        <is>
+          <t>All University risks including Risk 16 Climate Change were presented to RMCC and ARC in Nov 25 for their oversight.
+There will be a risk presentation of Risk 16 Climate Change at RMCC Meeting 1 in Feb 2026.</t>
+        </is>
+      </c>
+      <c r="I7" s="19" t="inlineStr">
+        <is>
+          <t>CL3(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="160" customHeight="1">
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>8a(ii)</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>The University reaches and maintains a 'high' climate change preparedness level</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>Case studies demonstrating climate change preparedness</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>Partially met</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="inlineStr"/>
+      <c r="G8" s="19" t="inlineStr">
+        <is>
+          <t>Flood Emergency Response Plans (FERP) for Southbank - MCM has been completed, while MTC is still in progress.
+The FERP for Creswick has also been completed and is awaiting review by FM Global.
+Case study -  In 2025, UoM received approximately $229k in resilience credits from FM Global, which can be applied to climate‑related projects.</t>
+        </is>
+      </c>
+      <c r="H8" s="19" t="inlineStr">
+        <is>
+          <t>As part of the University’s ongoing commitment to strengthening preparedness for climate‑related events, these FERPs will be reviewed regularly by both UoM  and FM Global. Ongoing training and awareness are also essential to ensuring the effectiveness of these plans.</t>
+        </is>
+      </c>
+      <c r="I8" s="19" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B3:I3"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="B4" location="'1. Reporting template'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/central_unit_requests/LandR - end-2026 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/LandR - end-2026 sustainability reporting request.xlsx
@@ -9,8 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Reporting template" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. OPTIONAL highlighted stories" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. SR25 responses" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. SR25 responses" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1135,217 +1135,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>End 2026 target status</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Data owner confirms</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Request status</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Y/N</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Target status</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Response count</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Please select from dropdown</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Not sent</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Sent</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Partially – see comments</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Chased</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Support meeting</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Under review</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Complete</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Not required</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1527,4 +1316,215 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>End 2026 target status</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Data owner confirms</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Request status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Y/N</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Target status</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Response count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Please select from dropdown</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Not sent</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Met or exceeded</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Met or exceeded</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Partially met</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Partially met</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Partially – see comments</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Chased</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Not met</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Not met</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Support meeting</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Not yet started</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Not yet started</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Under review</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Not required</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>